--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32363-2024 artfynd.xlsx
+++ b/artfynd/A 32363-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135856154</v>
       </c>
       <c r="B2" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
